--- a/spec-tech/ig/StructureDefinition-xdmAuthorDocumentEntry.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmAuthorDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T14:32:10+00:00</t>
+    <t>2026-07-23T16:03:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdmAuthorDocumentEntry.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmAuthorDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T16:03:49+00:00</t>
+    <t>2026-07-23T16:11:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdmAuthorDocumentEntry.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmAuthorDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T16:11:23+00:00</t>
+    <t>2026-07-27T13:36:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -86,8 +86,7 @@
 L’auteur peut être : 
 -  Un professionnel (personne physique) via son logiciel de professionnel, 
 - Le patient/usager (personne physique) via Mon espace Santé, 
--  Un système de structure (dispositif, automate, appareil connecté…), 
--  Un SNR (Service Numérique Référencé), </t>
+-  Un système de structure (dispositif, automate, appareil connecté…), </t>
   </si>
   <si>
     <t>Purpose</t>
@@ -288,7 +287,7 @@
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/xdmActorPs
-https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/xdmActorPatienthttps://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/xdmActorSnrhttps://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/xdmActorSystem</t>
+https://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/xdmActorPatienthttps://interop.esante.gouv.fr/ig/fhir/pdlgc/StructureDefinition/xdmActorSystem</t>
   </si>
   <si>
     <t>Cet attribut représente l’auteur (humain ou système) ayant contribué au document. Pour les documents d’expression personnelle du patient, cette métadonnée fait référence au patient.</t>
@@ -658,7 +657,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="185.20703125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="125.8125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/spec-tech/ig/StructureDefinition-xdmAuthorDocumentEntry.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmAuthorDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T13:36:25+00:00</t>
+    <t>2026-07-30T09:32:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdmAuthorDocumentEntry.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmAuthorDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T09:32:03+00:00</t>
+    <t>2026-07-30T15:04:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdmAuthorDocumentEntry.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmAuthorDocumentEntry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T15:04:16+00:00</t>
+    <t>2026-08-07T08:28:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
